--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120752140</v>
+        <v>120752132</v>
       </c>
       <c r="B8" t="n">
-        <v>79707</v>
+        <v>90705</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,38 +1341,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>MD85:Åre, SE-JA, SE, Jmt</t>
+          <t>MD0:830 02 Mattmar, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440366</v>
+        <v>440636</v>
       </c>
       <c r="R8" t="n">
-        <v>7001776</v>
+        <v>7001737</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120752132</v>
+        <v>120752140</v>
       </c>
       <c r="B9" t="n">
-        <v>90705</v>
+        <v>79707</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,38 +1453,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>MD0:830 02 Mattmar, Sweden, Jmt</t>
+          <t>MD85:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440636</v>
+        <v>440366</v>
       </c>
       <c r="R9" t="n">
-        <v>7001737</v>
+        <v>7001776</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1889,7 +1889,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120752412</v>
+        <v>120752137</v>
       </c>
       <c r="B13" t="n">
         <v>90705</v>
@@ -1925,17 +1925,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>MD0:Åre, SE-JA, SE, Jmt</t>
+          <t>MD88:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440498</v>
+        <v>440392</v>
       </c>
       <c r="R13" t="n">
-        <v>7001737</v>
+        <v>7001747</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1959,22 +1959,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,7 +2001,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120752137</v>
+        <v>120752412</v>
       </c>
       <c r="B14" t="n">
         <v>90705</v>
@@ -2037,17 +2037,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>MD88:Åre, SE-JA, SE, Jmt</t>
+          <t>MD0:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440392</v>
+        <v>440498</v>
       </c>
       <c r="R14" t="n">
-        <v>7001747</v>
+        <v>7001737</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,22 +2071,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120752130</v>
+        <v>120752141</v>
       </c>
       <c r="B15" t="n">
-        <v>105161</v>
+        <v>79707</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2129,34 +2129,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221725</v>
+        <v>6461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>MD96:Åre, SE-JA, SE, Jmt</t>
+          <t>MD83:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440628</v>
+        <v>440356</v>
       </c>
       <c r="R15" t="n">
-        <v>7001708</v>
+        <v>7001752</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,10 +2225,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120752141</v>
+        <v>120752130</v>
       </c>
       <c r="B16" t="n">
-        <v>79707</v>
+        <v>105161</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2241,34 +2241,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>MD83:Åre, SE-JA, SE, Jmt</t>
+          <t>MD96:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440356</v>
+        <v>440628</v>
       </c>
       <c r="R16" t="n">
-        <v>7001752</v>
+        <v>7001708</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120752411</v>
+        <v>120752137</v>
       </c>
       <c r="B5" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,17 +1029,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>MD1:Åre, SE-JA, SE, Jmt</t>
+          <t>MD88:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440447</v>
+        <v>440392</v>
       </c>
       <c r="R5" t="n">
-        <v>7001637</v>
+        <v>7001747</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,22 +1063,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120752127</v>
+        <v>120752124</v>
       </c>
       <c r="B6" t="n">
-        <v>97025</v>
+        <v>79711</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,37 +1121,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>MD98:Åre, SE-JA, SE, Jmt</t>
+          <t>MD105:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440702</v>
+        <v>440768</v>
       </c>
       <c r="R6" t="n">
-        <v>7001650</v>
+        <v>7001619</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120752147</v>
+        <v>120752412</v>
       </c>
       <c r="B7" t="n">
-        <v>91370</v>
+        <v>90715</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,38 +1229,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>MD78:Åre, SE-JA, SE, Jmt</t>
+          <t>MD0:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440406</v>
+        <v>440498</v>
       </c>
       <c r="R7" t="n">
-        <v>7001756</v>
+        <v>7001737</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1287,22 +1287,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120752132</v>
+        <v>120752411</v>
       </c>
       <c r="B8" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,14 +1365,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>MD0:830 02 Mattmar, Sweden, Jmt</t>
+          <t>MD1:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440636</v>
+        <v>440447</v>
       </c>
       <c r="R8" t="n">
-        <v>7001737</v>
+        <v>7001637</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1399,22 +1399,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120752140</v>
+        <v>120752117</v>
       </c>
       <c r="B9" t="n">
-        <v>79707</v>
+        <v>97035</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,37 +1457,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>MD85:Åre, SE-JA, SE, Jmt</t>
+          <t>MD107:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440366</v>
+        <v>440788</v>
       </c>
       <c r="R9" t="n">
-        <v>7001776</v>
+        <v>7001663</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120752124</v>
+        <v>120752132</v>
       </c>
       <c r="B10" t="n">
-        <v>79708</v>
+        <v>90715</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,41 +1565,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>MD105:Åre, SE-JA, SE, Jmt</t>
+          <t>MD0:830 02 Mattmar, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440768</v>
+        <v>440636</v>
       </c>
       <c r="R10" t="n">
-        <v>7001619</v>
+        <v>7001737</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120752117</v>
+        <v>120752140</v>
       </c>
       <c r="B11" t="n">
-        <v>97025</v>
+        <v>79710</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,37 +1681,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>MD107:Åre, SE-JA, SE, Jmt</t>
+          <t>MD85:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440788</v>
+        <v>440366</v>
       </c>
       <c r="R11" t="n">
-        <v>7001663</v>
+        <v>7001776</v>
       </c>
       <c r="S11" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1777,10 +1777,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120752120</v>
+        <v>120752141</v>
       </c>
       <c r="B12" t="n">
-        <v>56560</v>
+        <v>79710</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1793,34 +1793,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>MD104:Åre, SE-JA, SE, Jmt</t>
+          <t>MD83:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440738</v>
+        <v>440356</v>
       </c>
       <c r="R12" t="n">
-        <v>7001614</v>
+        <v>7001752</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1889,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120752137</v>
+        <v>120752127</v>
       </c>
       <c r="B13" t="n">
-        <v>90705</v>
+        <v>97035</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1901,41 +1901,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>MD88:Åre, SE-JA, SE, Jmt</t>
+          <t>MD98:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440392</v>
+        <v>440702</v>
       </c>
       <c r="R13" t="n">
-        <v>7001747</v>
+        <v>7001650</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120752412</v>
+        <v>120752130</v>
       </c>
       <c r="B14" t="n">
-        <v>90705</v>
+        <v>105171</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,38 +2013,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>MD0:Åre, SE-JA, SE, Jmt</t>
+          <t>MD96:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440498</v>
+        <v>440628</v>
       </c>
       <c r="R14" t="n">
-        <v>7001737</v>
+        <v>7001708</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2071,22 +2071,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120752141</v>
+        <v>120752147</v>
       </c>
       <c r="B15" t="n">
-        <v>79707</v>
+        <v>91380</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2129,34 +2129,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>MD83:Åre, SE-JA, SE, Jmt</t>
+          <t>MD78:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440356</v>
+        <v>440406</v>
       </c>
       <c r="R15" t="n">
-        <v>7001752</v>
+        <v>7001756</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,10 +2225,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120752130</v>
+        <v>120752120</v>
       </c>
       <c r="B16" t="n">
-        <v>105161</v>
+        <v>56563</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2241,34 +2241,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>MD96:Åre, SE-JA, SE, Jmt</t>
+          <t>MD104:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440628</v>
+        <v>440738</v>
       </c>
       <c r="R16" t="n">
-        <v>7001708</v>
+        <v>7001614</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2340,7 +2340,7 @@
         <v>120752405</v>
       </c>
       <c r="B17" t="n">
-        <v>79680</v>
+        <v>79683</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -1441,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120752117</v>
+        <v>120752132</v>
       </c>
       <c r="B9" t="n">
-        <v>97035</v>
+        <v>90715</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,41 +1453,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>MD107:Åre, SE-JA, SE, Jmt</t>
+          <t>MD0:830 02 Mattmar, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440788</v>
+        <v>440636</v>
       </c>
       <c r="R9" t="n">
-        <v>7001663</v>
+        <v>7001737</v>
       </c>
       <c r="S9" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120752132</v>
+        <v>120752117</v>
       </c>
       <c r="B10" t="n">
-        <v>90715</v>
+        <v>97035</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,41 +1565,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>MD0:830 02 Mattmar, Sweden, Jmt</t>
+          <t>MD107:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440636</v>
+        <v>440788</v>
       </c>
       <c r="R10" t="n">
-        <v>7001737</v>
+        <v>7001663</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120752137</v>
+        <v>120752140</v>
       </c>
       <c r="B5" t="n">
-        <v>90715</v>
+        <v>79710</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,41 +1005,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>MD88:Åre, SE-JA, SE, Jmt</t>
+          <t>MD85:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440392</v>
+        <v>440366</v>
       </c>
       <c r="R5" t="n">
-        <v>7001747</v>
+        <v>7001776</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1217,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120752412</v>
+        <v>120752120</v>
       </c>
       <c r="B7" t="n">
-        <v>90715</v>
+        <v>56563</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,38 +1229,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>MD0:Åre, SE-JA, SE, Jmt</t>
+          <t>MD104:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440498</v>
+        <v>440738</v>
       </c>
       <c r="R7" t="n">
-        <v>7001737</v>
+        <v>7001614</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1287,22 +1287,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120752411</v>
+        <v>120752117</v>
       </c>
       <c r="B8" t="n">
-        <v>90715</v>
+        <v>97035</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,41 +1341,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>MD1:Åre, SE-JA, SE, Jmt</t>
+          <t>MD107:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440447</v>
+        <v>440788</v>
       </c>
       <c r="R8" t="n">
-        <v>7001637</v>
+        <v>7001663</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,22 +1399,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120752132</v>
+        <v>120752127</v>
       </c>
       <c r="B9" t="n">
-        <v>90715</v>
+        <v>97035</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,38 +1453,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>MD0:830 02 Mattmar, Sweden, Jmt</t>
+          <t>MD98:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440636</v>
+        <v>440702</v>
       </c>
       <c r="R9" t="n">
-        <v>7001737</v>
+        <v>7001650</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120752117</v>
+        <v>120752147</v>
       </c>
       <c r="B10" t="n">
-        <v>97035</v>
+        <v>91380</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,37 +1569,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>MD107:Åre, SE-JA, SE, Jmt</t>
+          <t>MD78:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440788</v>
+        <v>440406</v>
       </c>
       <c r="R10" t="n">
-        <v>7001663</v>
+        <v>7001756</v>
       </c>
       <c r="S10" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120752140</v>
+        <v>120752412</v>
       </c>
       <c r="B11" t="n">
-        <v>79710</v>
+        <v>90715</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,38 +1677,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>MD85:Åre, SE-JA, SE, Jmt</t>
+          <t>MD0:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440366</v>
+        <v>440498</v>
       </c>
       <c r="R11" t="n">
-        <v>7001776</v>
+        <v>7001737</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1735,22 +1735,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1777,10 +1777,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120752141</v>
+        <v>120752411</v>
       </c>
       <c r="B12" t="n">
-        <v>79710</v>
+        <v>90715</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1789,38 +1789,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>MD83:Åre, SE-JA, SE, Jmt</t>
+          <t>MD1:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440356</v>
+        <v>440447</v>
       </c>
       <c r="R12" t="n">
-        <v>7001752</v>
+        <v>7001637</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1847,22 +1847,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1889,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120752127</v>
+        <v>120752405</v>
       </c>
       <c r="B13" t="n">
-        <v>97035</v>
+        <v>79683</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1901,41 +1901,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>MD98:Åre, SE-JA, SE, Jmt</t>
+          <t>MD1:830 02 Mattmar, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440702</v>
+        <v>440786</v>
       </c>
       <c r="R13" t="n">
-        <v>7001650</v>
+        <v>7001576</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1959,22 +1959,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hairy underside</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,10 +2006,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120752130</v>
+        <v>120752137</v>
       </c>
       <c r="B14" t="n">
-        <v>105171</v>
+        <v>90715</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,41 +2018,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>MD96:Åre, SE-JA, SE, Jmt</t>
+          <t>MD88:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440628</v>
+        <v>440392</v>
       </c>
       <c r="R14" t="n">
-        <v>7001708</v>
+        <v>7001747</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2076,7 +2081,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2086,7 +2091,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120752147</v>
+        <v>120752141</v>
       </c>
       <c r="B15" t="n">
-        <v>91380</v>
+        <v>79710</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2129,34 +2134,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>6461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>MD78:Åre, SE-JA, SE, Jmt</t>
+          <t>MD83:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440406</v>
+        <v>440356</v>
       </c>
       <c r="R15" t="n">
-        <v>7001756</v>
+        <v>7001752</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2188,7 +2193,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2198,7 +2203,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120752120</v>
+        <v>120752130</v>
       </c>
       <c r="B16" t="n">
-        <v>56563</v>
+        <v>105171</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2241,34 +2246,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>221725</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>MD104:Åre, SE-JA, SE, Jmt</t>
+          <t>MD96:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440738</v>
+        <v>440628</v>
       </c>
       <c r="R16" t="n">
-        <v>7001614</v>
+        <v>7001708</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2300,7 +2305,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2310,7 +2315,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,10 +2342,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120752405</v>
+        <v>120752132</v>
       </c>
       <c r="B17" t="n">
-        <v>79683</v>
+        <v>90715</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2353,37 +2358,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>MD1:830 02 Mattmar, Sweden, Jmt</t>
+          <t>MD0:830 02 Mattmar, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440786</v>
+        <v>440636</v>
       </c>
       <c r="R17" t="n">
-        <v>7001576</v>
+        <v>7001737</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2407,27 +2412,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hairy underside</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120752140</v>
+        <v>120752132</v>
       </c>
       <c r="B5" t="n">
-        <v>79710</v>
+        <v>90727</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>MD85:Åre, SE-JA, SE, Jmt</t>
+          <t>MD0:830 02 Mattmar, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440366</v>
+        <v>440636</v>
       </c>
       <c r="R5" t="n">
-        <v>7001776</v>
+        <v>7001737</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1108,7 @@
         <v>120752124</v>
       </c>
       <c r="B6" t="n">
-        <v>79711</v>
+        <v>79714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120752117</v>
+        <v>120752405</v>
       </c>
       <c r="B8" t="n">
-        <v>97035</v>
+        <v>79686</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,41 +1341,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>MD107:Åre, SE-JA, SE, Jmt</t>
+          <t>MD1:830 02 Mattmar, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440788</v>
+        <v>440786</v>
       </c>
       <c r="R8" t="n">
-        <v>7001663</v>
+        <v>7001576</v>
       </c>
       <c r="S8" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,22 +1399,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hairy underside</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,7 +1449,7 @@
         <v>120752127</v>
       </c>
       <c r="B9" t="n">
-        <v>97035</v>
+        <v>97048</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1553,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120752147</v>
+        <v>120752117</v>
       </c>
       <c r="B10" t="n">
-        <v>91380</v>
+        <v>97048</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,37 +1574,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>MD78:Åre, SE-JA, SE, Jmt</t>
+          <t>MD107:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440406</v>
+        <v>440788</v>
       </c>
       <c r="R10" t="n">
-        <v>7001756</v>
+        <v>7001663</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1638,7 +1643,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120752412</v>
+        <v>120752411</v>
       </c>
       <c r="B11" t="n">
-        <v>90715</v>
+        <v>90727</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,14 +1706,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>MD0:Åre, SE-JA, SE, Jmt</t>
+          <t>MD1:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440498</v>
+        <v>440447</v>
       </c>
       <c r="R11" t="n">
-        <v>7001737</v>
+        <v>7001637</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1740,7 +1745,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,7 +1755,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1777,10 +1782,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120752411</v>
+        <v>120752147</v>
       </c>
       <c r="B12" t="n">
-        <v>90715</v>
+        <v>91392</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1789,38 +1794,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>MD1:Åre, SE-JA, SE, Jmt</t>
+          <t>MD78:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440447</v>
+        <v>440406</v>
       </c>
       <c r="R12" t="n">
-        <v>7001637</v>
+        <v>7001756</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1847,22 +1852,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1889,10 +1894,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120752405</v>
+        <v>120752140</v>
       </c>
       <c r="B13" t="n">
-        <v>79683</v>
+        <v>79713</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1901,41 +1906,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>MD1:830 02 Mattmar, Sweden, Jmt</t>
+          <t>MD85:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440786</v>
+        <v>440366</v>
       </c>
       <c r="R13" t="n">
-        <v>7001576</v>
+        <v>7001776</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1959,27 +1964,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hairy underside</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,7 +2009,7 @@
         <v>120752137</v>
       </c>
       <c r="B14" t="n">
-        <v>90715</v>
+        <v>90727</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>120752141</v>
       </c>
       <c r="B15" t="n">
-        <v>79710</v>
+        <v>79713</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120752130</v>
+        <v>120752412</v>
       </c>
       <c r="B16" t="n">
-        <v>105171</v>
+        <v>90727</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2242,38 +2242,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>MD96:Åre, SE-JA, SE, Jmt</t>
+          <t>MD0:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440628</v>
+        <v>440498</v>
       </c>
       <c r="R16" t="n">
-        <v>7001708</v>
+        <v>7001737</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2300,22 +2300,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120752132</v>
+        <v>120752130</v>
       </c>
       <c r="B17" t="n">
-        <v>90715</v>
+        <v>105184</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2354,38 +2354,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>MD0:830 02 Mattmar, Sweden, Jmt</t>
+          <t>MD96:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440636</v>
+        <v>440628</v>
       </c>
       <c r="R17" t="n">
-        <v>7001737</v>
+        <v>7001708</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120752132</v>
+        <v>120752412</v>
       </c>
       <c r="B5" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,11 +1029,11 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>MD0:830 02 Mattmar, Sweden, Jmt</t>
+          <t>MD0:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440636</v>
+        <v>440498</v>
       </c>
       <c r="R5" t="n">
         <v>7001737</v>
@@ -1063,22 +1063,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120752124</v>
+        <v>120752147</v>
       </c>
       <c r="B6" t="n">
-        <v>79714</v>
+        <v>91393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,37 +1121,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>MD105:Åre, SE-JA, SE, Jmt</t>
+          <t>MD78:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440768</v>
+        <v>440406</v>
       </c>
       <c r="R6" t="n">
-        <v>7001619</v>
+        <v>7001756</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120752120</v>
+        <v>120752132</v>
       </c>
       <c r="B7" t="n">
-        <v>56563</v>
+        <v>90728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,38 +1229,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>MD104:Åre, SE-JA, SE, Jmt</t>
+          <t>MD0:830 02 Mattmar, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440738</v>
+        <v>440636</v>
       </c>
       <c r="R7" t="n">
-        <v>7001614</v>
+        <v>7001737</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120752405</v>
+        <v>120752117</v>
       </c>
       <c r="B8" t="n">
-        <v>79686</v>
+        <v>97049</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,41 +1341,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>MD1:830 02 Mattmar, Sweden, Jmt</t>
+          <t>MD107:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440786</v>
+        <v>440788</v>
       </c>
       <c r="R8" t="n">
-        <v>7001576</v>
+        <v>7001663</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,27 +1399,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hairy underside</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,7 +1444,7 @@
         <v>120752127</v>
       </c>
       <c r="B9" t="n">
-        <v>97048</v>
+        <v>97049</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1558,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120752117</v>
+        <v>120752141</v>
       </c>
       <c r="B10" t="n">
-        <v>97048</v>
+        <v>79713</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,37 +1569,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>MD107:Åre, SE-JA, SE, Jmt</t>
+          <t>MD83:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440788</v>
+        <v>440356</v>
       </c>
       <c r="R10" t="n">
-        <v>7001663</v>
+        <v>7001752</v>
       </c>
       <c r="S10" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1633,7 +1628,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1643,7 +1638,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,10 +1665,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120752411</v>
+        <v>120752140</v>
       </c>
       <c r="B11" t="n">
-        <v>90727</v>
+        <v>79713</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1682,38 +1677,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>MD1:Åre, SE-JA, SE, Jmt</t>
+          <t>MD85:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440447</v>
+        <v>440366</v>
       </c>
       <c r="R11" t="n">
-        <v>7001637</v>
+        <v>7001776</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1740,22 +1735,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,10 +1777,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120752147</v>
+        <v>120752137</v>
       </c>
       <c r="B12" t="n">
-        <v>91392</v>
+        <v>90728</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1794,41 +1789,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>MD78:Åre, SE-JA, SE, Jmt</t>
+          <t>MD88:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440406</v>
+        <v>440392</v>
       </c>
       <c r="R12" t="n">
-        <v>7001756</v>
+        <v>7001747</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1857,7 +1852,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1867,7 +1862,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120752140</v>
+        <v>120752120</v>
       </c>
       <c r="B13" t="n">
-        <v>79713</v>
+        <v>56563</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1910,34 +1905,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>MD85:Åre, SE-JA, SE, Jmt</t>
+          <t>MD104:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440366</v>
+        <v>440738</v>
       </c>
       <c r="R13" t="n">
-        <v>7001776</v>
+        <v>7001614</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1969,7 +1964,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1979,7 +1974,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,10 +2001,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120752137</v>
+        <v>120752124</v>
       </c>
       <c r="B14" t="n">
-        <v>90727</v>
+        <v>79714</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2018,41 +2013,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>MD88:Åre, SE-JA, SE, Jmt</t>
+          <t>MD105:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440392</v>
+        <v>440768</v>
       </c>
       <c r="R14" t="n">
-        <v>7001747</v>
+        <v>7001619</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2081,7 +2076,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2091,7 +2086,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120752141</v>
+        <v>120752405</v>
       </c>
       <c r="B15" t="n">
-        <v>79713</v>
+        <v>79686</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2130,41 +2125,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>MD83:Åre, SE-JA, SE, Jmt</t>
+          <t>MD1:830 02 Mattmar, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440356</v>
+        <v>440786</v>
       </c>
       <c r="R15" t="n">
-        <v>7001752</v>
+        <v>7001576</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2188,22 +2183,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hairy underside</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120752412</v>
+        <v>120752411</v>
       </c>
       <c r="B16" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2266,14 +2266,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>MD0:Åre, SE-JA, SE, Jmt</t>
+          <t>MD1:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440498</v>
+        <v>440447</v>
       </c>
       <c r="R16" t="n">
-        <v>7001737</v>
+        <v>7001637</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,7 +2345,7 @@
         <v>120752130</v>
       </c>
       <c r="B17" t="n">
-        <v>105184</v>
+        <v>105185</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120752412</v>
+        <v>120752140</v>
       </c>
       <c r="B5" t="n">
-        <v>90728</v>
+        <v>79716</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>MD0:Åre, SE-JA, SE, Jmt</t>
+          <t>MD85:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440498</v>
+        <v>440366</v>
       </c>
       <c r="R5" t="n">
-        <v>7001737</v>
+        <v>7001776</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1063,22 +1063,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120752147</v>
+        <v>120752411</v>
       </c>
       <c r="B6" t="n">
-        <v>91393</v>
+        <v>90731</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,38 +1117,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>MD78:Åre, SE-JA, SE, Jmt</t>
+          <t>MD1:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440406</v>
+        <v>440447</v>
       </c>
       <c r="R6" t="n">
-        <v>7001756</v>
+        <v>7001637</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1175,22 +1175,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120752132</v>
+        <v>120752405</v>
       </c>
       <c r="B7" t="n">
-        <v>90728</v>
+        <v>79689</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,37 +1233,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>MD0:830 02 Mattmar, Sweden, Jmt</t>
+          <t>MD1:830 02 Mattmar, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440636</v>
+        <v>440786</v>
       </c>
       <c r="R7" t="n">
-        <v>7001737</v>
+        <v>7001576</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,22 +1287,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hairy underside</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120752117</v>
+        <v>120752124</v>
       </c>
       <c r="B8" t="n">
-        <v>97049</v>
+        <v>79717</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,37 +1350,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>MD107:Åre, SE-JA, SE, Jmt</t>
+          <t>MD105:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440788</v>
+        <v>440768</v>
       </c>
       <c r="R8" t="n">
-        <v>7001663</v>
+        <v>7001619</v>
       </c>
       <c r="S8" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,7 +1409,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1414,7 +1419,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120752127</v>
+        <v>120752141</v>
       </c>
       <c r="B9" t="n">
-        <v>97049</v>
+        <v>79716</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,34 +1462,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>MD98:Åre, SE-JA, SE, Jmt</t>
+          <t>MD83:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440702</v>
+        <v>440356</v>
       </c>
       <c r="R9" t="n">
-        <v>7001650</v>
+        <v>7001752</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1516,7 +1521,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1526,7 +1531,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120752141</v>
+        <v>120752412</v>
       </c>
       <c r="B10" t="n">
-        <v>79713</v>
+        <v>90731</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,38 +1570,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>MD83:Åre, SE-JA, SE, Jmt</t>
+          <t>MD0:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440356</v>
+        <v>440498</v>
       </c>
       <c r="R10" t="n">
-        <v>7001752</v>
+        <v>7001737</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1623,22 +1628,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120752140</v>
+        <v>120752120</v>
       </c>
       <c r="B11" t="n">
-        <v>79713</v>
+        <v>56566</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1681,34 +1686,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>MD85:Åre, SE-JA, SE, Jmt</t>
+          <t>MD104:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440366</v>
+        <v>440738</v>
       </c>
       <c r="R11" t="n">
-        <v>7001776</v>
+        <v>7001614</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1740,7 +1745,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,7 +1755,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1777,10 +1782,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120752137</v>
+        <v>120752117</v>
       </c>
       <c r="B12" t="n">
-        <v>90728</v>
+        <v>97052</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1789,41 +1794,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>MD88:Åre, SE-JA, SE, Jmt</t>
+          <t>MD107:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440392</v>
+        <v>440788</v>
       </c>
       <c r="R12" t="n">
-        <v>7001747</v>
+        <v>7001663</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1852,7 +1857,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1862,7 +1867,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1889,10 +1894,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120752120</v>
+        <v>120752137</v>
       </c>
       <c r="B13" t="n">
-        <v>56563</v>
+        <v>90731</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1901,41 +1906,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>MD104:Åre, SE-JA, SE, Jmt</t>
+          <t>MD88:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440738</v>
+        <v>440392</v>
       </c>
       <c r="R13" t="n">
-        <v>7001614</v>
+        <v>7001747</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1964,7 +1969,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1974,7 +1979,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,10 +2006,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120752124</v>
+        <v>120752132</v>
       </c>
       <c r="B14" t="n">
-        <v>79714</v>
+        <v>90731</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,41 +2018,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>MD105:Åre, SE-JA, SE, Jmt</t>
+          <t>MD0:830 02 Mattmar, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440768</v>
+        <v>440636</v>
       </c>
       <c r="R14" t="n">
-        <v>7001619</v>
+        <v>7001737</v>
       </c>
       <c r="S14" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2076,7 +2081,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2086,7 +2091,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120752405</v>
+        <v>120752130</v>
       </c>
       <c r="B15" t="n">
-        <v>79686</v>
+        <v>105188</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2125,41 +2130,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>221725</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>MD1:830 02 Mattmar, Sweden, Jmt</t>
+          <t>MD96:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440786</v>
+        <v>440628</v>
       </c>
       <c r="R15" t="n">
-        <v>7001576</v>
+        <v>7001708</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2183,27 +2188,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hairy underside</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120752411</v>
+        <v>120752147</v>
       </c>
       <c r="B16" t="n">
-        <v>90728</v>
+        <v>91396</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2242,38 +2242,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>MD1:Åre, SE-JA, SE, Jmt</t>
+          <t>MD78:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440447</v>
+        <v>440406</v>
       </c>
       <c r="R16" t="n">
-        <v>7001637</v>
+        <v>7001756</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2300,22 +2300,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120752130</v>
+        <v>120752127</v>
       </c>
       <c r="B17" t="n">
-        <v>105185</v>
+        <v>97052</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2358,34 +2358,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>MD96:Åre, SE-JA, SE, Jmt</t>
+          <t>MD98:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440628</v>
+        <v>440702</v>
       </c>
       <c r="R17" t="n">
-        <v>7001708</v>
+        <v>7001650</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120752140</v>
+        <v>120752132</v>
       </c>
       <c r="B5" t="n">
-        <v>79716</v>
+        <v>90731</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>MD85:Åre, SE-JA, SE, Jmt</t>
+          <t>MD0:830 02 Mattmar, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440366</v>
+        <v>440636</v>
       </c>
       <c r="R5" t="n">
-        <v>7001776</v>
+        <v>7001737</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,7 +1105,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120752411</v>
+        <v>120752412</v>
       </c>
       <c r="B6" t="n">
         <v>90731</v>
@@ -1141,14 +1141,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>MD1:Åre, SE-JA, SE, Jmt</t>
+          <t>MD0:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440447</v>
+        <v>440498</v>
       </c>
       <c r="R6" t="n">
-        <v>7001637</v>
+        <v>7001737</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1334,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120752124</v>
+        <v>120752147</v>
       </c>
       <c r="B8" t="n">
-        <v>79717</v>
+        <v>91396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,37 +1350,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>MD105:Åre, SE-JA, SE, Jmt</t>
+          <t>MD78:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440768</v>
+        <v>440406</v>
       </c>
       <c r="R8" t="n">
-        <v>7001619</v>
+        <v>7001756</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1558,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120752412</v>
+        <v>120752140</v>
       </c>
       <c r="B10" t="n">
-        <v>90731</v>
+        <v>79716</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1570,38 +1570,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6461</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>MD0:Åre, SE-JA, SE, Jmt</t>
+          <t>MD85:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440498</v>
+        <v>440366</v>
       </c>
       <c r="R10" t="n">
-        <v>7001737</v>
+        <v>7001776</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1628,22 +1628,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120752120</v>
+        <v>120752137</v>
       </c>
       <c r="B11" t="n">
-        <v>56566</v>
+        <v>90731</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1682,41 +1682,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>MD104:Åre, SE-JA, SE, Jmt</t>
+          <t>MD88:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440738</v>
+        <v>440392</v>
       </c>
       <c r="R11" t="n">
-        <v>7001614</v>
+        <v>7001747</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,10 +1782,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120752117</v>
+        <v>120752120</v>
       </c>
       <c r="B12" t="n">
-        <v>97052</v>
+        <v>56566</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1798,37 +1798,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>MD107:Åre, SE-JA, SE, Jmt</t>
+          <t>MD104:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440788</v>
+        <v>440738</v>
       </c>
       <c r="R12" t="n">
-        <v>7001663</v>
+        <v>7001614</v>
       </c>
       <c r="S12" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,10 +1894,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120752137</v>
+        <v>120752127</v>
       </c>
       <c r="B13" t="n">
-        <v>90731</v>
+        <v>97052</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1906,41 +1906,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>MD88:Åre, SE-JA, SE, Jmt</t>
+          <t>MD98:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440392</v>
+        <v>440702</v>
       </c>
       <c r="R13" t="n">
-        <v>7001747</v>
+        <v>7001650</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,7 +2006,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120752132</v>
+        <v>120752411</v>
       </c>
       <c r="B14" t="n">
         <v>90731</v>
@@ -2042,14 +2042,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>MD0:830 02 Mattmar, Sweden, Jmt</t>
+          <t>MD1:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440636</v>
+        <v>440447</v>
       </c>
       <c r="R14" t="n">
-        <v>7001737</v>
+        <v>7001637</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2076,22 +2076,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,10 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120752130</v>
+        <v>120752117</v>
       </c>
       <c r="B15" t="n">
-        <v>105188</v>
+        <v>97052</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2134,37 +2134,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>MD96:Åre, SE-JA, SE, Jmt</t>
+          <t>MD107:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440628</v>
+        <v>440788</v>
       </c>
       <c r="R15" t="n">
-        <v>7001708</v>
+        <v>7001663</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120752147</v>
+        <v>120752124</v>
       </c>
       <c r="B16" t="n">
-        <v>91396</v>
+        <v>79717</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2246,37 +2246,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>MD78:Åre, SE-JA, SE, Jmt</t>
+          <t>MD105:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440406</v>
+        <v>440768</v>
       </c>
       <c r="R16" t="n">
-        <v>7001756</v>
+        <v>7001619</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2342,10 +2342,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120752127</v>
+        <v>120752130</v>
       </c>
       <c r="B17" t="n">
-        <v>97052</v>
+        <v>105188</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2358,34 +2358,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>MD98:Åre, SE-JA, SE, Jmt</t>
+          <t>MD96:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>440702</v>
+        <v>440628</v>
       </c>
       <c r="R17" t="n">
-        <v>7001650</v>
+        <v>7001708</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2452,6 +2452,536 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124800342</v>
+      </c>
+      <c r="B18" t="n">
+        <v>74906</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>440473</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7001464</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124800341</v>
+      </c>
+      <c r="B19" t="n">
+        <v>74906</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>440510</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7001642</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124800344</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91299</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>658</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>440437</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7001636</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124800345</v>
+      </c>
+      <c r="B21" t="n">
+        <v>82597</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>440416</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7001516</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124800343</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91030</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Västerfjället, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>440458</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7001639</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hallen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -2454,7 +2454,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800342</v>
+        <v>124800341</v>
       </c>
       <c r="B18" t="n">
         <v>74906</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440473</v>
+        <v>440510</v>
       </c>
       <c r="R18" t="n">
-        <v>7001464</v>
+        <v>7001642</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800341</v>
+        <v>124800345</v>
       </c>
       <c r="B19" t="n">
-        <v>74906</v>
+        <v>82597</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440510</v>
+        <v>440416</v>
       </c>
       <c r="R19" t="n">
-        <v>7001642</v>
+        <v>7001516</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800344</v>
+        <v>124800342</v>
       </c>
       <c r="B20" t="n">
-        <v>91299</v>
+        <v>74906</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,21 +2682,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440437</v>
+        <v>440473</v>
       </c>
       <c r="R20" t="n">
-        <v>7001636</v>
+        <v>7001464</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2772,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800345</v>
+        <v>124800344</v>
       </c>
       <c r="B21" t="n">
-        <v>82597</v>
+        <v>91299</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,21 +2788,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440416</v>
+        <v>440437</v>
       </c>
       <c r="R21" t="n">
-        <v>7001516</v>
+        <v>7001636</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -2454,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800341</v>
+        <v>124800343</v>
       </c>
       <c r="B18" t="n">
-        <v>74906</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,21 +2470,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440510</v>
+        <v>440458</v>
       </c>
       <c r="R18" t="n">
-        <v>7001642</v>
+        <v>7001639</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800345</v>
+        <v>124800342</v>
       </c>
       <c r="B19" t="n">
-        <v>82597</v>
+        <v>74906</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440416</v>
+        <v>440473</v>
       </c>
       <c r="R19" t="n">
-        <v>7001516</v>
+        <v>7001464</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800342</v>
+        <v>124800344</v>
       </c>
       <c r="B20" t="n">
-        <v>74906</v>
+        <v>91299</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,21 +2682,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440473</v>
+        <v>440437</v>
       </c>
       <c r="R20" t="n">
-        <v>7001464</v>
+        <v>7001636</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2772,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800344</v>
+        <v>124800345</v>
       </c>
       <c r="B21" t="n">
-        <v>91299</v>
+        <v>82597</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,21 +2788,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440437</v>
+        <v>440416</v>
       </c>
       <c r="R21" t="n">
-        <v>7001636</v>
+        <v>7001516</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2878,10 +2878,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800343</v>
+        <v>124800341</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>74906</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,21 +2894,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440458</v>
+        <v>440510</v>
       </c>
       <c r="R22" t="n">
-        <v>7001639</v>
+        <v>7001642</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -2454,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800343</v>
+        <v>124800342</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>74906</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,21 +2470,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440458</v>
+        <v>440473</v>
       </c>
       <c r="R18" t="n">
-        <v>7001639</v>
+        <v>7001464</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800342</v>
+        <v>124800343</v>
       </c>
       <c r="B19" t="n">
-        <v>74906</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440473</v>
+        <v>440458</v>
       </c>
       <c r="R19" t="n">
-        <v>7001464</v>
+        <v>7001639</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2772,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800345</v>
+        <v>124800341</v>
       </c>
       <c r="B21" t="n">
-        <v>82597</v>
+        <v>74906</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,21 +2788,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>1467</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440416</v>
+        <v>440510</v>
       </c>
       <c r="R21" t="n">
-        <v>7001516</v>
+        <v>7001642</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2878,10 +2878,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800341</v>
+        <v>124800345</v>
       </c>
       <c r="B22" t="n">
-        <v>74906</v>
+        <v>82597</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,21 +2894,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440510</v>
+        <v>440416</v>
       </c>
       <c r="R22" t="n">
-        <v>7001642</v>
+        <v>7001516</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -2560,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800343</v>
+        <v>124800345</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440458</v>
+        <v>440416</v>
       </c>
       <c r="R19" t="n">
-        <v>7001639</v>
+        <v>7001516</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2878,10 +2878,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800345</v>
+        <v>124800343</v>
       </c>
       <c r="B22" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,21 +2894,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440416</v>
+        <v>440458</v>
       </c>
       <c r="R22" t="n">
-        <v>7001516</v>
+        <v>7001639</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -2454,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800342</v>
+        <v>124800343</v>
       </c>
       <c r="B18" t="n">
-        <v>74906</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,21 +2470,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440473</v>
+        <v>440458</v>
       </c>
       <c r="R18" t="n">
-        <v>7001464</v>
+        <v>7001639</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800345</v>
+        <v>124800342</v>
       </c>
       <c r="B19" t="n">
-        <v>82597</v>
+        <v>74906</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440416</v>
+        <v>440473</v>
       </c>
       <c r="R19" t="n">
-        <v>7001516</v>
+        <v>7001464</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2878,10 +2878,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800343</v>
+        <v>124800345</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,21 +2894,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440458</v>
+        <v>440416</v>
       </c>
       <c r="R22" t="n">
-        <v>7001639</v>
+        <v>7001516</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -2454,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800343</v>
+        <v>124800345</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,21 +2470,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440458</v>
+        <v>440416</v>
       </c>
       <c r="R18" t="n">
-        <v>7001639</v>
+        <v>7001516</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,7 +2560,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800342</v>
+        <v>124800341</v>
       </c>
       <c r="B19" t="n">
         <v>74906</v>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440473</v>
+        <v>440510</v>
       </c>
       <c r="R19" t="n">
-        <v>7001464</v>
+        <v>7001642</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2772,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800341</v>
+        <v>124800343</v>
       </c>
       <c r="B21" t="n">
-        <v>74906</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,21 +2788,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440510</v>
+        <v>440458</v>
       </c>
       <c r="R21" t="n">
-        <v>7001642</v>
+        <v>7001639</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2878,10 +2878,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800345</v>
+        <v>124800342</v>
       </c>
       <c r="B22" t="n">
-        <v>82597</v>
+        <v>74906</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,21 +2894,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>1467</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440416</v>
+        <v>440473</v>
       </c>
       <c r="R22" t="n">
-        <v>7001516</v>
+        <v>7001464</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -2454,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800345</v>
+        <v>124800342</v>
       </c>
       <c r="B18" t="n">
-        <v>82597</v>
+        <v>74906</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,21 +2470,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440416</v>
+        <v>440473</v>
       </c>
       <c r="R18" t="n">
-        <v>7001516</v>
+        <v>7001464</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800341</v>
+        <v>124800344</v>
       </c>
       <c r="B19" t="n">
-        <v>74906</v>
+        <v>91299</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440510</v>
+        <v>440437</v>
       </c>
       <c r="R19" t="n">
-        <v>7001642</v>
+        <v>7001636</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800344</v>
+        <v>124800341</v>
       </c>
       <c r="B20" t="n">
-        <v>91299</v>
+        <v>74906</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,21 +2682,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440437</v>
+        <v>440510</v>
       </c>
       <c r="R20" t="n">
-        <v>7001636</v>
+        <v>7001642</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2878,10 +2878,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800342</v>
+        <v>124800345</v>
       </c>
       <c r="B22" t="n">
-        <v>74906</v>
+        <v>82597</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,21 +2894,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440473</v>
+        <v>440416</v>
       </c>
       <c r="R22" t="n">
-        <v>7001464</v>
+        <v>7001516</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -2454,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800342</v>
+        <v>124800345</v>
       </c>
       <c r="B18" t="n">
-        <v>74906</v>
+        <v>82597</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,21 +2470,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440473</v>
+        <v>440416</v>
       </c>
       <c r="R18" t="n">
-        <v>7001464</v>
+        <v>7001516</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800344</v>
+        <v>124800343</v>
       </c>
       <c r="B19" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440437</v>
+        <v>440458</v>
       </c>
       <c r="R19" t="n">
-        <v>7001636</v>
+        <v>7001639</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2666,7 +2666,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800341</v>
+        <v>124800342</v>
       </c>
       <c r="B20" t="n">
         <v>74906</v>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440510</v>
+        <v>440473</v>
       </c>
       <c r="R20" t="n">
-        <v>7001642</v>
+        <v>7001464</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2772,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800343</v>
+        <v>124800341</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>74906</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,21 +2788,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440458</v>
+        <v>440510</v>
       </c>
       <c r="R21" t="n">
-        <v>7001639</v>
+        <v>7001642</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2878,10 +2878,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800345</v>
+        <v>124800344</v>
       </c>
       <c r="B22" t="n">
-        <v>82597</v>
+        <v>91299</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,21 +2894,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440416</v>
+        <v>440437</v>
       </c>
       <c r="R22" t="n">
-        <v>7001516</v>
+        <v>7001636</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -2666,7 +2666,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800342</v>
+        <v>124800341</v>
       </c>
       <c r="B20" t="n">
         <v>74906</v>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440473</v>
+        <v>440510</v>
       </c>
       <c r="R20" t="n">
-        <v>7001464</v>
+        <v>7001642</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2772,7 +2772,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800341</v>
+        <v>124800342</v>
       </c>
       <c r="B21" t="n">
         <v>74906</v>
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440510</v>
+        <v>440473</v>
       </c>
       <c r="R21" t="n">
-        <v>7001642</v>
+        <v>7001464</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -2454,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800345</v>
+        <v>124800344</v>
       </c>
       <c r="B18" t="n">
-        <v>82597</v>
+        <v>91299</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,21 +2470,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440416</v>
+        <v>440437</v>
       </c>
       <c r="R18" t="n">
-        <v>7001516</v>
+        <v>7001636</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800343</v>
+        <v>124800345</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440458</v>
+        <v>440416</v>
       </c>
       <c r="R19" t="n">
-        <v>7001639</v>
+        <v>7001516</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2772,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800342</v>
+        <v>124800343</v>
       </c>
       <c r="B21" t="n">
-        <v>74906</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,21 +2788,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440473</v>
+        <v>440458</v>
       </c>
       <c r="R21" t="n">
-        <v>7001464</v>
+        <v>7001639</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2878,10 +2878,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800344</v>
+        <v>124800342</v>
       </c>
       <c r="B22" t="n">
-        <v>91299</v>
+        <v>74906</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,21 +2894,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1467</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440437</v>
+        <v>440473</v>
       </c>
       <c r="R22" t="n">
-        <v>7001636</v>
+        <v>7001464</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -2454,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800344</v>
+        <v>124800341</v>
       </c>
       <c r="B18" t="n">
-        <v>91299</v>
+        <v>74906</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,21 +2470,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1467</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440437</v>
+        <v>440510</v>
       </c>
       <c r="R18" t="n">
-        <v>7001636</v>
+        <v>7001642</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800345</v>
+        <v>124800343</v>
       </c>
       <c r="B19" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440416</v>
+        <v>440458</v>
       </c>
       <c r="R19" t="n">
-        <v>7001516</v>
+        <v>7001639</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800341</v>
+        <v>124800344</v>
       </c>
       <c r="B20" t="n">
-        <v>74906</v>
+        <v>91299</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,21 +2682,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440510</v>
+        <v>440437</v>
       </c>
       <c r="R20" t="n">
-        <v>7001642</v>
+        <v>7001636</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2772,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800343</v>
+        <v>124800342</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>74906</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,21 +2788,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440458</v>
+        <v>440473</v>
       </c>
       <c r="R21" t="n">
-        <v>7001639</v>
+        <v>7001464</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2878,10 +2878,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800342</v>
+        <v>124800345</v>
       </c>
       <c r="B22" t="n">
-        <v>74906</v>
+        <v>82597</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,21 +2894,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440473</v>
+        <v>440416</v>
       </c>
       <c r="R22" t="n">
-        <v>7001464</v>
+        <v>7001516</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -2454,7 +2454,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800341</v>
+        <v>124800342</v>
       </c>
       <c r="B18" t="n">
         <v>74906</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440510</v>
+        <v>440473</v>
       </c>
       <c r="R18" t="n">
-        <v>7001642</v>
+        <v>7001464</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800343</v>
+        <v>124800341</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>74906</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440458</v>
+        <v>440510</v>
       </c>
       <c r="R19" t="n">
-        <v>7001639</v>
+        <v>7001642</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2772,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800342</v>
+        <v>124800343</v>
       </c>
       <c r="B21" t="n">
-        <v>74906</v>
+        <v>91030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,21 +2788,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1467</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440473</v>
+        <v>440458</v>
       </c>
       <c r="R21" t="n">
-        <v>7001464</v>
+        <v>7001639</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -2454,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800342</v>
+        <v>124800344</v>
       </c>
       <c r="B18" t="n">
-        <v>74906</v>
+        <v>91459</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,21 +2470,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1467</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440473</v>
+        <v>440437</v>
       </c>
       <c r="R18" t="n">
-        <v>7001464</v>
+        <v>7001636</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800341</v>
+        <v>124800345</v>
       </c>
       <c r="B19" t="n">
-        <v>74906</v>
+        <v>82737</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440510</v>
+        <v>440416</v>
       </c>
       <c r="R19" t="n">
-        <v>7001642</v>
+        <v>7001516</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800344</v>
+        <v>124800341</v>
       </c>
       <c r="B20" t="n">
-        <v>91299</v>
+        <v>75030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,21 +2682,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440437</v>
+        <v>440510</v>
       </c>
       <c r="R20" t="n">
-        <v>7001636</v>
+        <v>7001642</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2772,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800343</v>
+        <v>124800342</v>
       </c>
       <c r="B21" t="n">
-        <v>91030</v>
+        <v>75030</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,21 +2788,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440458</v>
+        <v>440473</v>
       </c>
       <c r="R21" t="n">
-        <v>7001639</v>
+        <v>7001464</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2878,10 +2878,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800345</v>
+        <v>124800343</v>
       </c>
       <c r="B22" t="n">
-        <v>82597</v>
+        <v>91184</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,21 +2894,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440416</v>
+        <v>440458</v>
       </c>
       <c r="R22" t="n">
-        <v>7001516</v>
+        <v>7001639</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -2454,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800344</v>
+        <v>124800343</v>
       </c>
       <c r="B18" t="n">
-        <v>91459</v>
+        <v>91184</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,21 +2470,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440437</v>
+        <v>440458</v>
       </c>
       <c r="R18" t="n">
-        <v>7001636</v>
+        <v>7001639</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2560,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800345</v>
+        <v>124800341</v>
       </c>
       <c r="B19" t="n">
-        <v>82737</v>
+        <v>75030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440416</v>
+        <v>440510</v>
       </c>
       <c r="R19" t="n">
-        <v>7001516</v>
+        <v>7001642</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800341</v>
+        <v>124800345</v>
       </c>
       <c r="B20" t="n">
-        <v>75030</v>
+        <v>82737</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,21 +2682,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440510</v>
+        <v>440416</v>
       </c>
       <c r="R20" t="n">
-        <v>7001642</v>
+        <v>7001516</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2772,10 +2772,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124800342</v>
+        <v>124800344</v>
       </c>
       <c r="B21" t="n">
-        <v>75030</v>
+        <v>91459</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,21 +2788,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1467</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>440473</v>
+        <v>440437</v>
       </c>
       <c r="R21" t="n">
-        <v>7001464</v>
+        <v>7001636</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2878,10 +2878,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124800343</v>
+        <v>124800342</v>
       </c>
       <c r="B22" t="n">
-        <v>91184</v>
+        <v>75030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2894,21 +2894,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>440458</v>
+        <v>440473</v>
       </c>
       <c r="R22" t="n">
-        <v>7001639</v>
+        <v>7001464</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120743825</v>
+        <v>124800344</v>
       </c>
       <c r="B2" t="n">
-        <v>90682</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storostflon, Storostflon, Jmt</t>
+          <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440645</v>
+        <v>440437</v>
       </c>
       <c r="R2" t="n">
-        <v>7001692</v>
+        <v>7001636</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +764,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rashid Kadhim, Jonny Daborg</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120741122</v>
+        <v>120751828</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,49 +787,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102125</v>
+        <v>863</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Mörk blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Hypogymnia austerodes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Räsänen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storostflon, Storostflon, Jmt</t>
+          <t>Storostflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440286</v>
+        <v>440611</v>
       </c>
       <c r="R3" t="n">
-        <v>7001625</v>
+        <v>7001911</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,12 +852,18 @@
           <t>2024-10-29</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På torrträd vid myr/hällmarkskant. På samma träd växer också knottrig blåslav.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,53 +882,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120743822</v>
+        <v>120751823</v>
       </c>
       <c r="B4" t="n">
-        <v>91026</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2062</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storostflon, Storostflon, Jmt</t>
+          <t>Storostflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440643</v>
+        <v>440611</v>
       </c>
       <c r="R4" t="n">
-        <v>7001693</v>
+        <v>7001911</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,6 +964,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120752132</v>
+        <v>120743825</v>
       </c>
       <c r="B5" t="n">
-        <v>90731</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,37 +994,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>MD0:830 02 Mattmar, Sweden, Jmt</t>
+          <t>Storostflon, Storostflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440636</v>
+        <v>440645</v>
       </c>
       <c r="R5" t="n">
-        <v>7001737</v>
+        <v>7001692</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,22 +1048,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,27 +1068,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120752412</v>
+        <v>124800345</v>
       </c>
       <c r="B6" t="n">
-        <v>90731</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,37 +1091,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>MD0:Åre, SE-JA, SE, Jmt</t>
+          <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440498</v>
+        <v>440416</v>
       </c>
       <c r="R6" t="n">
-        <v>7001737</v>
+        <v>7001516</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,22 +1149,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,27 +1169,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120752405</v>
+        <v>124800341</v>
       </c>
       <c r="B7" t="n">
-        <v>79689</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1233,37 +1192,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>MD1:830 02 Mattmar, Sweden, Jmt</t>
+          <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>440786</v>
+        <v>440510</v>
       </c>
       <c r="R7" t="n">
-        <v>7001576</v>
+        <v>7001642</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,27 +1250,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:07</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hairy underside</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,65 +1270,64 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120752147</v>
+        <v>124800342</v>
       </c>
       <c r="B8" t="n">
-        <v>91396</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>MD78:Åre, SE-JA, SE, Jmt</t>
+          <t>Västerfjället, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>440406</v>
+        <v>440473</v>
       </c>
       <c r="R8" t="n">
-        <v>7001756</v>
+        <v>7001464</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,22 +1351,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:50</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:50</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,65 +1371,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120752141</v>
+        <v>120743822</v>
       </c>
       <c r="B9" t="n">
-        <v>79716</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6461</v>
+        <v>2062</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>MD83:Åre, SE-JA, SE, Jmt</t>
+          <t>Storostflon, Storostflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>440356</v>
+        <v>440643</v>
       </c>
       <c r="R9" t="n">
-        <v>7001752</v>
+        <v>7001693</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1516,22 +1448,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:33</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:33</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,65 +1468,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120752140</v>
+        <v>120752405</v>
       </c>
       <c r="B10" t="n">
-        <v>79716</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6461</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>MD85:Åre, SE-JA, SE, Jmt</t>
+          <t>MD1:830 02 Mattmar, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>440366</v>
+        <v>440786</v>
       </c>
       <c r="R10" t="n">
-        <v>7001776</v>
+        <v>7001576</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,22 +1545,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-09-29</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hairy underside</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,53 +1592,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120752137</v>
+        <v>120752147</v>
       </c>
       <c r="B11" t="n">
-        <v>90731</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>MD88:Åre, SE-JA, SE, Jmt</t>
+          <t>MD78:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>440392</v>
+        <v>440406</v>
       </c>
       <c r="R11" t="n">
-        <v>7001747</v>
+        <v>7001756</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1745,7 +1662,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1755,7 +1672,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,15 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120752120</v>
+        <v>120752140</v>
       </c>
       <c r="B12" t="n">
-        <v>56566</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1798,34 +1710,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>MD104:Åre, SE-JA, SE, Jmt</t>
+          <t>MD85:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>440738</v>
+        <v>440366</v>
       </c>
       <c r="R12" t="n">
-        <v>7001614</v>
+        <v>7001776</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1857,7 +1769,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1867,7 +1779,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,15 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120752127</v>
+        <v>120752141</v>
       </c>
       <c r="B13" t="n">
-        <v>97052</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,34 +1817,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>MD98:Åre, SE-JA, SE, Jmt</t>
+          <t>MD83:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>440702</v>
+        <v>440356</v>
       </c>
       <c r="R13" t="n">
-        <v>7001650</v>
+        <v>7001752</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1969,7 +1876,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1979,7 +1886,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,53 +1913,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120752411</v>
+        <v>120752124</v>
       </c>
       <c r="B14" t="n">
-        <v>90731</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>MD1:Åre, SE-JA, SE, Jmt</t>
+          <t>MD105:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>440447</v>
+        <v>440768</v>
       </c>
       <c r="R14" t="n">
-        <v>7001637</v>
+        <v>7001619</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2076,22 +1978,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-29</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2118,15 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120752117</v>
+        <v>120752120</v>
       </c>
       <c r="B15" t="n">
-        <v>97052</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2134,37 +2031,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>MD107:Åre, SE-JA, SE, Jmt</t>
+          <t>MD104:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>440788</v>
+        <v>440738</v>
       </c>
       <c r="R15" t="n">
-        <v>7001663</v>
+        <v>7001614</v>
       </c>
       <c r="S15" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2193,7 +2090,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2203,7 +2100,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,15 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120752124</v>
+        <v>120741122</v>
       </c>
       <c r="B16" t="n">
-        <v>79717</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58592</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2246,37 +2138,49 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>102125</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>MD105:Åre, SE-JA, SE, Jmt</t>
+          <t>Storostflon, Storostflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>440768</v>
+        <v>440286</v>
       </c>
       <c r="R16" t="n">
-        <v>7001619</v>
+        <v>7001625</v>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2300,22 +2204,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:11</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:11</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2330,12 +2224,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Rashid Kadhim, Jonny Daborg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2345,12 +2239,7 @@
         <v>120752130</v>
       </c>
       <c r="B17" t="n">
-        <v>105188</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2454,57 +2343,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124800343</v>
+        <v>120752117</v>
       </c>
       <c r="B18" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västerfjället, Jmt</t>
+          <t>MD107:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>440458</v>
+        <v>440788</v>
       </c>
       <c r="R18" t="n">
-        <v>7001639</v>
+        <v>7001663</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2528,12 +2408,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2548,69 +2438,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124800341</v>
+        <v>120752127</v>
       </c>
       <c r="B19" t="n">
-        <v>75030</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Västerfjället, Jmt</t>
+          <t>MD98:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>440510</v>
+        <v>440702</v>
       </c>
       <c r="R19" t="n">
-        <v>7001642</v>
+        <v>7001650</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2634,12 +2515,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,69 +2545,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124800345</v>
+        <v>120752175</v>
       </c>
       <c r="B20" t="n">
-        <v>82737</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Västerfjället, Jmt</t>
+          <t>MD51:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>440416</v>
+        <v>440606</v>
       </c>
       <c r="R20" t="n">
-        <v>7001516</v>
+        <v>7002043</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2740,12 +2622,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2024-05-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2760,227 +2652,15 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>124800344</v>
-      </c>
-      <c r="B21" t="n">
-        <v>91459</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>658</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Västerfjället, Jmt</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>440437</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7001636</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>124800342</v>
-      </c>
-      <c r="B22" t="n">
-        <v>75030</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>1467</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Rödbrun blekspik</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Sclerophora coniophaea</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Västerfjället, Jmt</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>440473</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7001464</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2025-05-04</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13097-2024 artfynd.xlsx
+++ b/artfynd/A 13097-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800344</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120751828</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120751823</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120743825</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800345</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800341</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124800342</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1477,6 +1517,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120743822</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1589,6 +1634,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120752405</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1696,6 +1746,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120752147</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1803,6 +1858,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120752140</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1910,6 +1970,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120752141</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2017,6 +2082,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120752124</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2124,6 +2194,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120752120</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2233,6 +2308,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120741122</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2340,6 +2420,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120752130</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2447,6 +2532,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120752117</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2554,6 +2644,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120752127</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2661,8 +2756,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120752175</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>